--- a/artfynd/A 10819-2024 artfynd.xlsx
+++ b/artfynd/A 10819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96483491</v>
+        <v>109716188</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566700.3184620334</v>
+        <v>566804</v>
       </c>
       <c r="R2" t="n">
-        <v>6618315.099531887</v>
+        <v>6618247</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gick på landsvägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -801,6 +796,814 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131095184</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58420</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102992</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Näktergal</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Luscinia luscinia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västersjön, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566598</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6618323</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122460152</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566804</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618247</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96483483</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566707</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618330</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96483491</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566700</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618315</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96483614</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566686</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618335</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96585316</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566688</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96585330</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Borgåsen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566673</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618346</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10819-2024 artfynd.xlsx
+++ b/artfynd/A 10819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109716188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131095184</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122460152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483483</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483614</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96585316</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,8 +1644,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96585330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>